--- a/kospi200.xlsx
+++ b/kospi200.xlsx
@@ -469,32 +469,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>183,000</t>
+          <t>180,100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락8,900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10,744,550</t>
+          <t>30,096,671</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1,979,477</t>
+          <t>5,485,512</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,832,937</t>
+          <t>10,661,268</t>
         </is>
       </c>
     </row>
@@ -509,32 +509,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>955,000</t>
+          <t>933,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>하락40,000</t>
+          <t>하락62,000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-6.23%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,322,642</t>
+          <t>4,275,572</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,272,799</t>
+          <t>4,053,991</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6,806,308</t>
+          <t>6,649,513</t>
         </is>
       </c>
     </row>
@@ -549,32 +549,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>495,000</t>
+          <t>489,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락12,000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.20%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>253,237</t>
+          <t>899,183</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>125,350</t>
+          <t>442,067</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1,013,551</t>
+          <t>1,001,265</t>
         </is>
       </c>
     </row>
@@ -589,32 +589,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>381,500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하락7,000</t>
+          <t>하락12,500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69,774</t>
+          <t>258,878</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27,199</t>
+          <t>100,017</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>905,580</t>
+          <t>892,710</t>
         </is>
       </c>
     </row>
@@ -629,32 +629,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>573,000</t>
+          <t>558,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>하락32,000</t>
+          <t>하락47,000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.29%</t>
+          <t>-7.77%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>178,122</t>
+          <t>549,439</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>103,339</t>
+          <t>313,569</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>756,859</t>
+          <t>737,046</t>
         </is>
       </c>
     </row>
@@ -669,32 +669,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1,592,000</t>
+          <t>1,582,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상승7,000</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7,877</t>
+          <t>26,275</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12,612</t>
+          <t>41,915</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>736,952</t>
+          <t>732,323</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1,413,500</t>
+          <t>1,367,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>상승13,500</t>
+          <t>하락33,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,473</t>
+          <t>147,373</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>75,323</t>
+          <t>205,003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>728,849</t>
+          <t>704,872</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>102,100</t>
+          <t>100,800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,800</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>753,817</t>
+          <t>2,444,003</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>77,285</t>
+          <t>248,025</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>654,013</t>
+          <t>645,686</t>
         </is>
       </c>
     </row>
@@ -789,32 +789,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>156,300</t>
+          <t>154,600</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락3,300</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>253,723</t>
+          <t>712,543</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>39,545</t>
+          <t>110,877</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>610,216</t>
+          <t>603,578</t>
         </is>
       </c>
     </row>
@@ -829,32 +829,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>151,600</t>
+          <t>152,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>상승2,200</t>
+          <t>상승2,600</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>297,112</t>
+          <t>904,744</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>44,953</t>
+          <t>137,448</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>565,241</t>
+          <t>566,733</t>
         </is>
       </c>
     </row>
@@ -869,32 +869,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>523,000</t>
+          <t>511,000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락12,000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52,989</t>
+          <t>164,893</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27,702</t>
+          <t>85,335</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>548,947</t>
+          <t>536,352</t>
         </is>
       </c>
     </row>
@@ -909,32 +909,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>285,000</t>
+          <t>276,500</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>하락4,000</t>
+          <t>하락12,500</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88,776</t>
+          <t>325,172</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25,516</t>
+          <t>91,190</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>484,433</t>
+          <t>469,985</t>
         </is>
       </c>
     </row>
@@ -949,32 +949,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>204,250</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>상승750</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>132,676</t>
+          <t>395,912</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27,260</t>
+          <t>80,761</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>471,916</t>
+          <t>466,717</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>224,500</t>
+          <t>221,500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락6,000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53,845</t>
+          <t>342,943</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12,170</t>
+          <t>77,043</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>449,000</t>
+          <t>443,000</t>
         </is>
       </c>
     </row>
@@ -1029,32 +1029,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>93,500</t>
+          <t>92,900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>상승1,400</t>
+          <t>상승800</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>225,103</t>
+          <t>823,368</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20,996</t>
+          <t>77,056</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>443,802</t>
+          <t>440,954</t>
         </is>
       </c>
     </row>
@@ -1069,32 +1069,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>128,000</t>
+          <t>125,600</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>상승3,300</t>
+          <t>상승900</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>420,042</t>
+          <t>893,658</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>53,985</t>
+          <t>113,742</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>392,209</t>
+          <t>384,855</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>67,500</t>
+          <t>65,300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>상승200</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1,730,800</t>
+          <t>3,522,095</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>117,277</t>
+          <t>236,408</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>374,839</t>
+          <t>362,622</t>
         </is>
       </c>
     </row>
@@ -1149,32 +1149,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>398,500</t>
+          <t>396,500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51,797</t>
+          <t>175,942</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20,616</t>
+          <t>70,043</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>361,569</t>
+          <t>359,755</t>
         </is>
       </c>
     </row>
@@ -1189,32 +1189,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>980,000</t>
+          <t>965,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>하락12,000</t>
+          <t>하락27,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26,884</t>
+          <t>69,686</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>26,594</t>
+          <t>68,252</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>353,262</t>
+          <t>347,855</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>196,967</t>
+          <t>465,060</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>90,384</t>
+          <t>212,525</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1269,32 +1269,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>215,500</t>
+          <t>211,500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>99,756</t>
+          <t>346,879</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21,536</t>
+          <t>74,222</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>338,017</t>
+          <t>331,743</t>
         </is>
       </c>
     </row>
@@ -1304,37 +1304,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>405,000</t>
+          <t>1,533,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>하락60,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>161,420</t>
+          <t>14,384</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65,749</t>
+          <t>22,295</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>326,371</t>
+          <t>319,983</t>
         </is>
       </c>
     </row>
@@ -1344,37 +1344,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>393,500</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>하락33,000</t>
+          <t>하락10,500</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3,979</t>
+          <t>425,621</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6,253</t>
+          <t>171,232</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>325,618</t>
+          <t>317,104</t>
         </is>
       </c>
     </row>
@@ -1389,32 +1389,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>109,300</t>
+          <t>108,500</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>186,103</t>
+          <t>662,009</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20,304</t>
+          <t>72,341</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>304,210</t>
+          <t>301,984</t>
         </is>
       </c>
     </row>
@@ -1429,32 +1429,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>46,250</t>
+          <t>45,700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락750</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>499,376</t>
+          <t>1,411,915</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23,020</t>
+          <t>65,022</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>296,908</t>
+          <t>293,378</t>
         </is>
       </c>
     </row>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>347,000</t>
+          <t>341,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>100,511</t>
+          <t>234,690</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>34,935</t>
+          <t>81,061</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>280,837</t>
+          <t>275,981</t>
         </is>
       </c>
     </row>
@@ -1504,37 +1504,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>2,856,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락134,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-2.00%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>145,737</t>
+          <t>41,647</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>42,835</t>
+          <t>121,464</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>280,218</t>
+          <t>266,309</t>
         </is>
       </c>
     </row>
@@ -1544,37 +1544,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2,906,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>하락84,000</t>
+          <t>하락21,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>-7.00%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15,364</t>
+          <t>609,371</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>45,700</t>
+          <t>175,130</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>270,971</t>
+          <t>265,921</t>
         </is>
       </c>
     </row>
@@ -1589,32 +1589,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>382,500</t>
+          <t>373,500</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락11,500</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>53,701</t>
+          <t>152,609</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20,656</t>
+          <t>58,026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>270,707</t>
+          <t>264,338</t>
         </is>
       </c>
     </row>
@@ -1624,37 +1624,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>135,800</t>
+          <t>834,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>371,363</t>
+          <t>88,471</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50,195</t>
+          <t>74,544</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>256,553</t>
+          <t>250,200</t>
         </is>
       </c>
     </row>
@@ -1664,37 +1664,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LS ELECTRIC</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>847,000</t>
+          <t>129,700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>하락6,900</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25,093</t>
+          <t>849,000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21,338</t>
+          <t>113,139</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>254,100</t>
+          <t>245,028</t>
         </is>
       </c>
     </row>
@@ -1709,32 +1709,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>335,500</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>하락10,500</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>38,315</t>
+          <t>160,974</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13,338</t>
+          <t>55,310</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>253,034</t>
+          <t>243,247</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>222,608</t>
+          <t>1,297,752</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7,351</t>
+          <t>43,173</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>상승150</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1,008,718</t>
+          <t>2,415,216</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27,400</t>
+          <t>64,823</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>237,600</t>
+          <t>231,880</t>
         </is>
       </c>
     </row>
@@ -1829,32 +1829,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>319,500</t>
+          <t>311,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>상승1,500</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-2.20%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>55,835</t>
+          <t>195,864</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>62,157</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>225,543</t>
+          <t>219,542</t>
         </is>
       </c>
     </row>
@@ -1869,32 +1869,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>49,250</t>
+          <t>48,600</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>상승200</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>303,932</t>
+          <t>1,140,245</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14,978</t>
+          <t>55,874</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>218,062</t>
+          <t>215,184</t>
         </is>
       </c>
     </row>
@@ -1909,32 +1909,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>272,000</t>
+          <t>265,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>상승7,000</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34,592</t>
+          <t>104,078</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9,317</t>
+          <t>27,999</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>214,861</t>
+          <t>209,332</t>
         </is>
       </c>
     </row>
@@ -1944,37 +1944,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>194,500</t>
+          <t>450,500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>상승3,800</t>
+          <t>하락39,500</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-8.06%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>254,388</t>
+          <t>112,116</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>48,746</t>
+          <t>51,476</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>212,282</t>
+          <t>207,280</t>
         </is>
       </c>
     </row>
@@ -1984,37 +1984,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>459,500</t>
+          <t>189,200</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>하락30,500</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-6.22%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>38,325</t>
+          <t>605,291</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17,849</t>
+          <t>115,990</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>211,421</t>
+          <t>206,497</t>
         </is>
       </c>
     </row>
@@ -2029,32 +2029,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1,251,000</t>
+          <t>1,238,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>하락12,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>15,543</t>
+          <t>47,905</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19,395</t>
+          <t>59,542</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>202,585</t>
+          <t>200,480</t>
         </is>
       </c>
     </row>
@@ -2069,32 +2069,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>116,800</t>
+          <t>114,100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>상승5,400</t>
+          <t>상승2,700</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+4.85%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>83,901</t>
+          <t>313,879</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>9,606</t>
+          <t>36,223</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>197,393</t>
+          <t>192,830</t>
         </is>
       </c>
     </row>
@@ -2109,32 +2109,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>112,000</t>
+          <t>110,700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>하락2,100</t>
+          <t>하락3,400</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>75,023</t>
+          <t>278,159</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8,435</t>
+          <t>31,191</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>189,339</t>
+          <t>187,141</t>
         </is>
       </c>
     </row>
@@ -2149,32 +2149,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>19,870</t>
+          <t>19,790</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>하락60</t>
+          <t>하락140</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>471,657</t>
+          <t>2,090,851</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9,404</t>
+          <t>41,593</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>187,421</t>
+          <t>186,667</t>
         </is>
       </c>
     </row>
@@ -2189,32 +2189,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>23,350</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>180,679</t>
+          <t>1,089,289</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4,240</t>
+          <t>25,611</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>187,395</t>
+          <t>186,199</t>
         </is>
       </c>
     </row>
@@ -2229,32 +2229,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>112,600</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>하락2,100</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>125,757</t>
+          <t>522,743</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14,351</t>
+          <t>59,039</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>185,690</t>
+          <t>183,410</t>
         </is>
       </c>
     </row>
@@ -2269,32 +2269,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>189,900</t>
+          <t>187,000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>상승4,900</t>
+          <t>상승2,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>278,653</t>
+          <t>673,494</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>52,357</t>
+          <t>126,614</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>185,105</t>
+          <t>182,278</t>
         </is>
       </c>
     </row>
@@ -2304,37 +2304,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>206,500</t>
+          <t>155,300</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>하락600</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>117,225</t>
+          <t>183,365</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24,299</t>
+          <t>28,816</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>183,674</t>
+          <t>178,093</t>
         </is>
       </c>
     </row>
@@ -2344,37 +2344,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>156,300</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>상승400</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>43,430</t>
+          <t>275,795</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6,825</t>
+          <t>56,407</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>179,240</t>
+          <t>177,892</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2389,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>80,800</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>상승200</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>244,716</t>
+          <t>756,807</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19,750</t>
+          <t>61,149</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>173,550</t>
+          <t>171,832</t>
         </is>
       </c>
     </row>
@@ -2429,32 +2429,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>229,000</t>
+          <t>226,500</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>22,638</t>
+          <t>79,240</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5,192</t>
+          <t>18,058</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>171,750</t>
+          <t>169,875</t>
         </is>
       </c>
     </row>
@@ -2469,32 +2469,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>154,000</t>
+          <t>152,400</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>하락3,900</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>257,500</t>
+          <t>642,753</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>40,052</t>
+          <t>98,994</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>171,488</t>
+          <t>169,706</t>
         </is>
       </c>
     </row>
@@ -2509,32 +2509,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>760,000</t>
+          <t>735,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>상승26,000</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>189,873</t>
+          <t>409,018</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>142,256</t>
+          <t>305,301</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>167,200</t>
+          <t>161,700</t>
         </is>
       </c>
     </row>
@@ -2549,32 +2549,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>60,700</t>
+          <t>59,750</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락350</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>71,092</t>
+          <t>258,218</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4,302</t>
+          <t>15,642</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>152,977</t>
+          <t>150,583</t>
         </is>
       </c>
     </row>
@@ -2584,37 +2584,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>88,400</t>
+          <t>78,100</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>상승2,300</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>68,609</t>
+          <t>1,027,230</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6,048</t>
+          <t>79,462</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>136,332</t>
+          <t>137,396</t>
         </is>
       </c>
     </row>
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>삼성에피스홀딩스</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>541,000</t>
+          <t>87,600</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>상승1,000</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>16,502</t>
+          <t>173,382</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9,028</t>
+          <t>15,277</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>134,617</t>
+          <t>135,098</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2664,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>삼성에피스홀딩스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>76,100</t>
+          <t>532,000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>하락8,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>132,124</t>
+          <t>47,709</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>9,964</t>
+          <t>25,664</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>133,877</t>
+          <t>132,378</t>
         </is>
       </c>
     </row>
@@ -2709,32 +2709,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>309,500</t>
+          <t>304,000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>상승5,000</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>+1.64%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>131,891</t>
+          <t>364,781</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>40,502</t>
+          <t>111,715</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>133,295</t>
+          <t>130,926</t>
         </is>
       </c>
     </row>
@@ -2749,32 +2749,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>112,900</t>
+          <t>112,800</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70,776</t>
+          <t>282,637</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7,962</t>
+          <t>31,909</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>127,106</t>
+          <t>126,993</t>
         </is>
       </c>
     </row>
@@ -2789,32 +2789,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>178,300</t>
+          <t>175,800</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>하락16,400</t>
+          <t>하락18,900</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-8.42%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>74,625</t>
+          <t>349,868</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>13,587</t>
+          <t>62,369</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>123,712</t>
+          <t>121,977</t>
         </is>
       </c>
     </row>
@@ -2829,32 +2829,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>159,000</t>
+          <t>155,500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>18,866</t>
+          <t>126,790</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3,001</t>
+          <t>19,945</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>123,031</t>
+          <t>120,322</t>
         </is>
       </c>
     </row>
@@ -2864,37 +2864,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>한국금융지주</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>326,500</t>
+          <t>214,500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락6,000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>90,895</t>
+          <t>172,698</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29,834</t>
+          <t>37,441</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>122,236</t>
+          <t>119,532</t>
         </is>
       </c>
     </row>
@@ -2904,37 +2904,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>33,300</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>46,478</t>
+          <t>698,487</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10,153</t>
+          <t>23,499</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>122,040</t>
+          <t>118,663</t>
         </is>
       </c>
     </row>
@@ -2944,37 +2944,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>33,800</t>
+          <t>24,350</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>176,847</t>
+          <t>501,673</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6,009</t>
+          <t>12,274</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>120,444</t>
+          <t>116,160</t>
         </is>
       </c>
     </row>
@@ -2984,37 +2984,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>310,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>하락50</t>
+          <t>하락18,500</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>126,783</t>
+          <t>391,602</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3,104</t>
+          <t>124,527</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>116,876</t>
+          <t>116,058</t>
         </is>
       </c>
     </row>
@@ -3029,32 +3029,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>244,500</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>33,138</t>
+          <t>118,648</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8,094</t>
+          <t>29,084</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>115,908</t>
+          <t>113,775</t>
         </is>
       </c>
     </row>
@@ -3069,32 +3069,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>430,500</t>
+          <t>416,500</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락15,500</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>19,422</t>
+          <t>58,681</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8,311</t>
+          <t>24,819</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>112,841</t>
+          <t>109,172</t>
         </is>
       </c>
     </row>
@@ -3109,32 +3109,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>397,500</t>
+          <t>387,500</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>하락8,000</t>
+          <t>하락18,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>19,127</t>
+          <t>58,168</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7,632</t>
+          <t>22,931</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>109,010</t>
+          <t>106,268</t>
         </is>
       </c>
     </row>
@@ -3149,32 +3149,32 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>25,100</t>
+          <t>24,950</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>309,928</t>
+          <t>1,127,616</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7,781</t>
+          <t>28,277</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>92,423</t>
+          <t>91,871</t>
         </is>
       </c>
     </row>
@@ -3189,32 +3189,32 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1,210,000</t>
+          <t>1,185,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락31,000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10,108</t>
+          <t>34,956</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>12,353</t>
+          <t>42,208</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>91,149</t>
+          <t>89,266</t>
         </is>
       </c>
     </row>
@@ -3224,37 +3224,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>121,000</t>
+          <t>277,000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>상승4,300</t>
+          <t>하락6,500</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>67,814</t>
+          <t>136,887</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8,085</t>
+          <t>38,631</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>90,700</t>
+          <t>86,424</t>
         </is>
       </c>
     </row>
@@ -3264,37 +3264,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>285,500</t>
+          <t>94,700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>상승2,000</t>
+          <t>하락3,100</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>40,257</t>
+          <t>256,148</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>11,528</t>
+          <t>24,587</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>89,076</t>
+          <t>84,567</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3309,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>118,600</t>
+          <t>114,900</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락5,400</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>279,720</t>
+          <t>675,206</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>33,125</t>
+          <t>79,262</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>87,063</t>
+          <t>84,347</t>
         </is>
       </c>
     </row>
@@ -3344,37 +3344,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>97,100</t>
+          <t>111,000</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>하락5,700</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>54,294</t>
+          <t>362,286</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5,279</t>
+          <t>41,597</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>86,710</t>
+          <t>83,204</t>
         </is>
       </c>
     </row>
@@ -3384,37 +3384,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>123,100</t>
+          <t>178,500</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>하락3,600</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>27,059</t>
+          <t>55,225</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3,338</t>
+          <t>9,915</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>82,184</t>
+          <t>80,024</t>
         </is>
       </c>
     </row>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>180,300</t>
+          <t>135,700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3439,22 +3439,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13,713</t>
+          <t>113,339</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2,479</t>
+          <t>15,565</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>80,831</t>
+          <t>79,375</t>
         </is>
       </c>
     </row>
@@ -3464,37 +3464,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>137,900</t>
+          <t>118,200</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>상승1,100</t>
+          <t>하락8,500</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>+0.80%</t>
+          <t>-6.71%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>32,133</t>
+          <t>98,952</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4,416</t>
+          <t>11,967</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>80,662</t>
+          <t>78,913</t>
         </is>
       </c>
     </row>
@@ -3509,32 +3509,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>100,200</t>
+          <t>98,600</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>상승1,300</t>
+          <t>하락300</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>78,067</t>
+          <t>178,952</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7,839</t>
+          <t>17,872</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>79,807</t>
+          <t>78,533</t>
         </is>
       </c>
     </row>
@@ -3544,37 +3544,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>44,750</t>
+          <t>94,700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>893,019</t>
+          <t>196,313</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>40,488</t>
+          <t>18,830</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>76,922</t>
+          <t>74,163</t>
         </is>
       </c>
     </row>
@@ -3584,37 +3584,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>96,500</t>
+          <t>303,500</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>하락9,500</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>54,549</t>
+          <t>189,517</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>5,324</t>
+          <t>58,786</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>75,572</t>
+          <t>71,830</t>
         </is>
       </c>
     </row>
@@ -3624,37 +3624,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>한국타이어앤테크놀로지</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>313,000</t>
+          <t>57,200</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락900</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>78,857</t>
+          <t>265,689</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>24,835</t>
+          <t>15,301</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>74,078</t>
+          <t>70,857</t>
         </is>
       </c>
     </row>
@@ -3664,37 +3664,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>564,000</t>
+          <t>52,300</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>상승23,000</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>+4.25%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>31,895</t>
+          <t>390,715</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17,628</t>
+          <t>20,669</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>72,254</t>
+          <t>70,722</t>
         </is>
       </c>
     </row>
@@ -3704,37 +3704,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>53,200</t>
+          <t>550,000</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>상승9,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+1.66%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>117,948</t>
+          <t>103,073</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6,319</t>
+          <t>57,493</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>71,939</t>
+          <t>70,460</t>
         </is>
       </c>
     </row>
@@ -3744,37 +3744,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>한국타이어앤테크놀로지</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>57,900</t>
+          <t>15,960</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>상승360</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61,759</t>
+          <t>769,591</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3,577</t>
+          <t>12,283</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>71,724</t>
+          <t>68,601</t>
         </is>
       </c>
     </row>
@@ -3784,37 +3784,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>15,940</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>상승400</t>
+          <t>하락470</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>186,056</t>
+          <t>18,006,568</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2,940</t>
+          <t>289,537</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>68,773</t>
+          <t>66,250</t>
         </is>
       </c>
     </row>
@@ -3824,37 +3824,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>16,290</t>
+          <t>32,850</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>하락120</t>
+          <t>하락850</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>7,659,625</t>
+          <t>2,332,679</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>122,927</t>
+          <t>77,486</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>67,705</t>
+          <t>64,386</t>
         </is>
       </c>
     </row>
@@ -3864,37 +3864,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>32,750</t>
+          <t>54,400</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>하락950</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-3.55%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>741,630</t>
+          <t>123,197</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>24,422</t>
+          <t>6,746</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>64,190</t>
+          <t>63,027</t>
         </is>
       </c>
     </row>
@@ -3904,37 +3904,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>68,900</t>
+          <t>36,600</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락8,400</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-18.67%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>43,453</t>
+          <t>10,226,336</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3,007</t>
+          <t>396,262</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>64,019</t>
+          <t>62,913</t>
         </is>
       </c>
     </row>
@@ -3944,37 +3944,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>54,700</t>
+          <t>67,700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락2,500</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>36,501</t>
+          <t>195,918</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2,018</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>63,375</t>
+          <t>62,904</t>
         </is>
       </c>
     </row>
@@ -3989,32 +3989,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>165,700</t>
+          <t>163,400</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>하락3,100</t>
+          <t>하락5,400</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>44,131</t>
+          <t>139,134</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7,349</t>
+          <t>22,945</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>63,331</t>
+          <t>62,451</t>
         </is>
       </c>
     </row>
@@ -4024,37 +4024,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>207,500</t>
+          <t>61,300</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17,080</t>
+          <t>350,925</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3,583</t>
+          <t>21,685</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>60,542</t>
+          <t>59,391</t>
         </is>
       </c>
     </row>
@@ -4064,37 +4064,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>203,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락7,000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>112,924</t>
+          <t>63,530</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7,026</t>
+          <t>13,156</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>60,069</t>
+          <t>59,229</t>
         </is>
       </c>
     </row>
@@ -4104,37 +4104,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>두산밥캣</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>61,500</t>
+          <t>144,200</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락1,100</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>57,790</t>
+          <t>1,023,516</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3,558</t>
+          <t>148,566</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>58,951</t>
+          <t>58,144</t>
         </is>
       </c>
     </row>
@@ -4149,32 +4149,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>11,770</t>
+          <t>11,520</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>상승20</t>
+          <t>하락230</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>770,691</t>
+          <t>2,580,341</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9,010</t>
+          <t>30,086</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>58,850</t>
+          <t>57,600</t>
         </is>
       </c>
     </row>
@@ -4184,37 +4184,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>두산밥캣</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>145,200</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>417,334</t>
+          <t>212,131</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>60,333</t>
+          <t>12,969</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>58,547</t>
+          <t>57,514</t>
         </is>
       </c>
     </row>
@@ -4229,32 +4229,32 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>18,670</t>
+          <t>18,450</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>상승220</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>110,714</t>
+          <t>501,820</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2,055</t>
+          <t>9,309</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>57,938</t>
+          <t>57,255</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4269,32 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>30,150</t>
+          <t>29,950</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>상승300</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>+1.69%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60,418</t>
+          <t>250,288</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1,806</t>
+          <t>7,542</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>56,758</t>
+          <t>56,382</t>
         </is>
       </c>
     </row>
@@ -4309,32 +4309,32 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>87,200</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>하락1,600</t>
+          <t>하락3,800</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>37,237</t>
+          <t>123,370</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>3,251</t>
+          <t>10,657</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>56,523</t>
+          <t>55,097</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>29,100</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>679,044</t>
+          <t>1,722,018</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20,521</t>
+          <t>51,076</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>55,561</t>
+          <t>54,256</t>
         </is>
       </c>
     </row>
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>173,700</t>
+          <t>132,100</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>상승7,900</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>+4.76%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>342,695</t>
+          <t>129,049</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>59,994</t>
+          <t>17,121</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>53,057</t>
+          <t>52,227</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>133,200</t>
+          <t>73,200</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4439,22 +4439,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>23,812</t>
+          <t>152,609</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>3,166</t>
+          <t>11,210</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>52,662</t>
+          <t>51,802</t>
         </is>
       </c>
     </row>
@@ -4464,37 +4464,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>73,400</t>
+          <t>167,600</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>상승1,800</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41,145</t>
+          <t>570,408</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>3,027</t>
+          <t>98,710</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>51,943</t>
+          <t>51,194</t>
         </is>
       </c>
     </row>
@@ -4509,32 +4509,32 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>72,200</t>
+          <t>69,950</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>상승1,800</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>764,360</t>
+          <t>1,892,723</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>54,474</t>
+          <t>135,105</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>50,943</t>
+          <t>49,356</t>
         </is>
       </c>
     </row>
@@ -4549,32 +4549,32 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>224,500</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>25,517</t>
+          <t>86,815</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5,809</t>
+          <t>19,652</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>48,474</t>
+          <t>48,366</t>
         </is>
       </c>
     </row>
@@ -4584,37 +4584,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>포스코DX</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>31,200</t>
+          <t>34,850</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락850</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>58,182</t>
+          <t>502,132</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1,830</t>
+          <t>17,753</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>47,435</t>
+          <t>46,506</t>
         </is>
       </c>
     </row>
@@ -4624,37 +4624,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>35,750</t>
+          <t>523,000</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>하락10,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>134,121</t>
+          <t>18,939</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4,761</t>
+          <t>9,876</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>47,707</t>
+          <t>46,476</t>
         </is>
       </c>
     </row>
@@ -4664,37 +4664,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>525,000</t>
+          <t>30,350</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>하락8,000</t>
+          <t>하락1,150</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>-1.50%</t>
+          <t>-3.65%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>3,101</t>
+          <t>321,568</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1,629</t>
+          <t>9,886</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>46,654</t>
+          <t>46,143</t>
         </is>
       </c>
     </row>
@@ -4704,37 +4704,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>51,400</t>
+          <t>51,500</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>상승2,650</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>573,682</t>
+          <t>169,237</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>29,810</t>
+          <t>8,801</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>42,892</t>
+          <t>42,210</t>
         </is>
       </c>
     </row>
@@ -4744,37 +4744,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>4,727</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락243</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-4.89%</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>58,738</t>
+          <t>5,356,575</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>3,079</t>
+          <t>25,875</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>42,619</t>
+          <t>41,055</t>
         </is>
       </c>
     </row>
@@ -4784,37 +4784,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4,870</t>
+          <t>49,050</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>상승300</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1,950,298</t>
+          <t>936,741</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>9,529</t>
+          <t>47,875</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>42,297</t>
+          <t>40,931</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3,940</t>
+          <t>3,890</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>하락115</t>
+          <t>하락165</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2,355,916</t>
+          <t>5,194,251</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>9,342</t>
+          <t>20,440</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>40,435</t>
+          <t>39,922</t>
         </is>
       </c>
     </row>
@@ -4869,32 +4869,32 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>18,150</t>
+          <t>18,240</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>상승10</t>
+          <t>상승100</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>111,138</t>
+          <t>708,817</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2,015</t>
+          <t>12,932</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>38,830</t>
+          <t>39,023</t>
         </is>
       </c>
     </row>
@@ -4909,32 +4909,32 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>100,700</t>
+          <t>98,000</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>하락4,100</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>29,822</t>
+          <t>115,035</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>3,010</t>
+          <t>11,468</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>38,133</t>
+          <t>37,111</t>
         </is>
       </c>
     </row>
@@ -4949,32 +4949,32 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>243,500</t>
+          <t>241,500</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>하락3,000</t>
+          <t>하락5,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>7,669</t>
+          <t>28,650</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1,869</t>
+          <t>6,956</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>37,261</t>
+          <t>36,955</t>
         </is>
       </c>
     </row>
@@ -4989,32 +4989,32 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>82,900</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>상승1,100</t>
+          <t>하락800</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>11,292</t>
+          <t>37,008</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>3,030</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>36,734</t>
+          <t>35,892</t>
         </is>
       </c>
     </row>
@@ -5029,32 +5029,32 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>188,500</t>
+          <t>184,500</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>상승5,700</t>
+          <t>상승1,700</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>111,309</t>
+          <t>221,502</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>21,439</t>
+          <t>41,831</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>35,193</t>
+          <t>34,447</t>
         </is>
       </c>
     </row>
@@ -5064,37 +5064,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>87,300</t>
+          <t>80,400</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>25,611</t>
+          <t>256,003</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2,242</t>
+          <t>20,796</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>34,128</t>
+          <t>34,391</t>
         </is>
       </c>
     </row>
@@ -5104,37 +5104,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>43,300</t>
+          <t>86,700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>20,412</t>
+          <t>135,774</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>11,846</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>33,962</t>
+          <t>33,893</t>
         </is>
       </c>
     </row>
@@ -5144,37 +5144,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>79,400</t>
+          <t>64,300</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>하락400</t>
+          <t>상승6,400</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>+11.05%</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>42,032</t>
+          <t>1,355,328</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>3,352</t>
+          <t>86,242</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>33,964</t>
+          <t>33,591</t>
         </is>
       </c>
     </row>
@@ -5184,37 +5184,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>64,600</t>
+          <t>42,650</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>상승6,700</t>
+          <t>하락150</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>+11.57%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>602,420</t>
+          <t>66,329</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>37,494</t>
+          <t>2,850</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>33,747</t>
+          <t>33,452</t>
         </is>
       </c>
     </row>
@@ -5224,37 +5224,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>128,800</t>
+          <t>87,200</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>하락1,200</t>
+          <t>상승300</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>11,948</t>
+          <t>40,911</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1,542</t>
+          <t>3,580</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>33,529</t>
+          <t>33,135</t>
         </is>
       </c>
     </row>
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>금호석유화학</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>87,400</t>
+          <t>127,100</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>상승500</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>10,380</t>
+          <t>68,312</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>8,781</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>33,211</t>
+          <t>33,086</t>
         </is>
       </c>
     </row>
@@ -5309,32 +5309,32 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>35,700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락300</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>36,254</t>
+          <t>138,970</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1,305</t>
+          <t>4,989</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>33,233</t>
+          <t>32,956</t>
         </is>
       </c>
     </row>
@@ -5349,32 +5349,32 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>218,500</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락4,000</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>6,909</t>
+          <t>27,117</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1,504</t>
+          <t>5,899</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>32,893</t>
+          <t>32,366</t>
         </is>
       </c>
     </row>
@@ -5384,37 +5384,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>287,000</t>
+          <t>114,100</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>상승4,500</t>
+          <t>상승2,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>13,888</t>
+          <t>169,870</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3,992</t>
+          <t>19,512</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>32,632</t>
+          <t>32,277</t>
         </is>
       </c>
     </row>
@@ -5424,37 +5424,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>롯데지주</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>114,700</t>
+          <t>30,500</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>상승3,400</t>
+          <t>하락600</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>36,728</t>
+          <t>265,789</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4,193</t>
+          <t>8,148</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>32,447</t>
+          <t>31,997</t>
         </is>
       </c>
     </row>
@@ -5464,37 +5464,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>333,500</t>
+          <t>281,000</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>하락1,500</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>4,415</t>
+          <t>38,311</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1,474</t>
+          <t>10,933</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>32,167</t>
+          <t>31,950</t>
         </is>
       </c>
     </row>
@@ -5504,37 +5504,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>롯데지주</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>30,550</t>
+          <t>329,500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>하락550</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-1.77%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>67,293</t>
+          <t>23,506</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2,060</t>
+          <t>7,801</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>32,050</t>
+          <t>31,781</t>
         </is>
       </c>
     </row>
@@ -5549,32 +5549,32 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>223,500</t>
+          <t>217,000</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>상승3,000</t>
+          <t>하락3,500</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>10,096</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2,236</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>30,171</t>
+          <t>29,293</t>
         </is>
       </c>
     </row>
@@ -5584,37 +5584,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>94,200</t>
+          <t>31,150</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>상승3,200</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>144,315</t>
+          <t>429,914</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>13,597</t>
+          <t>13,438</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>28,466</t>
+          <t>27,848</t>
         </is>
       </c>
     </row>
@@ -5624,37 +5624,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>81,800</t>
+          <t>91,600</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>상승4,300</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>+5.55%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>327,074</t>
+          <t>313,126</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>26,879</t>
+          <t>29,316</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>27,748</t>
+          <t>27,680</t>
         </is>
       </c>
     </row>
@@ -5669,32 +5669,32 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>59,700</t>
+          <t>59,100</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>22,882</t>
+          <t>121,221</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1,368</t>
+          <t>7,174</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>27,730</t>
+          <t>27,451</t>
         </is>
       </c>
     </row>
@@ -5704,37 +5704,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>17,020</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>하락1,250</t>
+          <t>상승40</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>-3.89%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>152,110</t>
+          <t>433,858</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4,759</t>
+          <t>7,443</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>27,625</t>
+          <t>27,338</t>
         </is>
       </c>
     </row>
@@ -5749,32 +5749,32 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>61,300</t>
+          <t>60,600</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>하락1,500</t>
+          <t>하락2,200</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61,268</t>
+          <t>173,491</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>3,771</t>
+          <t>10,611</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>27,585</t>
+          <t>27,270</t>
         </is>
       </c>
     </row>
@@ -5784,37 +5784,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>동서</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>27,100</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>상승20</t>
+          <t>하락100</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>53,635</t>
+          <t>61,849</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>1,677</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>27,306</t>
+          <t>27,019</t>
         </is>
       </c>
     </row>
@@ -5824,37 +5824,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>풍산</t>
+          <t>이마트</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>96,500</t>
+          <t>97,800</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>63,377</t>
+          <t>137,836</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>6,121</t>
+          <t>13,459</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>27,043</t>
+          <t>26,989</t>
         </is>
       </c>
     </row>
@@ -5864,37 +5864,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>이마트</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>97,700</t>
+          <t>4,980</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락100</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>47,447</t>
+          <t>2,972,922</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4,629</t>
+          <t>14,817</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>26,961</t>
+          <t>26,622</t>
         </is>
       </c>
     </row>
@@ -5904,37 +5904,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>동서</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>78,400</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>상승900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>17,955</t>
+          <t>502,306</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>40,879</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>26,919</t>
+          <t>26,594</t>
         </is>
       </c>
     </row>
@@ -5944,37 +5944,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>풍산</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>5,010</t>
+          <t>93,500</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>하락70</t>
+          <t>하락4,700</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>480,396</t>
+          <t>208,496</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2,421</t>
+          <t>19,853</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>26,782</t>
+          <t>26,203</t>
         </is>
       </c>
     </row>
@@ -5989,32 +5989,32 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>63,400</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>227,411</t>
+          <t>574,097</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>14,377</t>
+          <t>36,314</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>26,737</t>
+          <t>26,146</t>
         </is>
       </c>
     </row>
@@ -6029,32 +6029,32 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>38,400</t>
+          <t>37,700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>상승700</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>+1.86%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>30,553</t>
+          <t>105,834</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1,167</t>
+          <t>4,019</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>26,262</t>
+          <t>25,784</t>
         </is>
       </c>
     </row>
@@ -6069,32 +6069,32 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>66,100</t>
+          <t>66,400</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>하락3,200</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>-4.62%</t>
+          <t>-4.18%</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>742,747</t>
+          <t>1,555,030</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>49,936</t>
+          <t>103,535</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>25,576</t>
+          <t>25,693</t>
         </is>
       </c>
     </row>
@@ -6109,32 +6109,32 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>26,800</t>
+          <t>26,750</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락850</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>-2.90%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>21,210</t>
+          <t>81,777</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>2,198</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>25,443</t>
+          <t>25,395</t>
         </is>
       </c>
     </row>
@@ -6149,32 +6149,32 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>70,600</t>
+          <t>69,900</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>하락1,900</t>
+          <t>하락2,600</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-2.62%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>99,581</t>
+          <t>223,324</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>7,064</t>
+          <t>15,783</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>25,319</t>
+          <t>25,068</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6189,32 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>110,300</t>
+          <t>107,700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>하락1,800</t>
+          <t>하락4,400</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>6,007</t>
+          <t>65,399</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>7,090</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>25,162</t>
+          <t>24,569</t>
         </is>
       </c>
     </row>
@@ -6229,32 +6229,32 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>51,800</t>
+          <t>51,300</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락1,100</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-2.10%</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>46,655</t>
+          <t>163,680</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2,422</t>
+          <t>8,438</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>24,324</t>
+          <t>24,089</t>
         </is>
       </c>
     </row>
@@ -6264,37 +6264,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>61,500</t>
+          <t>41,150</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>하락1,300</t>
+          <t>상승1,950</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>+4.97%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>17,582</t>
+          <t>404,222</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>1,085</t>
+          <t>16,344</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>23,559</t>
+          <t>24,077</t>
         </is>
       </c>
     </row>
@@ -6304,37 +6304,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>20,050</t>
+          <t>62,100</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락700</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>67,827</t>
+          <t>58,571</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1,360</t>
+          <t>3,621</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>23,066</t>
+          <t>23,789</t>
         </is>
       </c>
     </row>
@@ -6344,37 +6344,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>39,350</t>
+          <t>19,760</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>상승150</t>
+          <t>하락290</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>51,866</t>
+          <t>508,313</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2,035</t>
+          <t>10,105</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>23,024</t>
+          <t>22,732</t>
         </is>
       </c>
     </row>
@@ -6389,32 +6389,32 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>374,500</t>
+          <t>373,000</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>하락4,000</t>
+          <t>하락5,500</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>4,272</t>
+          <t>17,946</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1,601</t>
+          <t>6,721</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>22,779</t>
+          <t>22,688</t>
         </is>
       </c>
     </row>
@@ -6429,32 +6429,32 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>26,700</t>
+          <t>26,200</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-4.38%</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>715,887</t>
+          <t>1,697,175</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>19,030</t>
+          <t>44,911</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>22,850</t>
+          <t>22,422</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>코오롱인더</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>43,250</t>
+          <t>80,200</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6479,22 +6479,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>644,281</t>
+          <t>629,451</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>28,214</t>
+          <t>51,643</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>22,450</t>
+          <t>22,070</t>
         </is>
       </c>
     </row>
@@ -6504,37 +6504,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>현대위아</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>82,100</t>
+          <t>42,400</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>상승550</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>20,693</t>
+          <t>1,033,748</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1,699</t>
+          <t>44,862</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>22,327</t>
+          <t>22,009</t>
         </is>
       </c>
     </row>
@@ -6544,37 +6544,37 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>코오롱인더</t>
+          <t>현대위아</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>81,400</t>
+          <t>80,900</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>상승2,600</t>
+          <t>하락1,700</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>+3.30%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>153,860</t>
+          <t>92,618</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>12,407</t>
+          <t>7,547</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>22,401</t>
+          <t>22,001</t>
         </is>
       </c>
     </row>
@@ -6584,37 +6584,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>192,800</t>
+          <t>125,000</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>하락3,500</t>
+          <t>상승2,100</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>10,427</t>
+          <t>29,940</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2,030</t>
+          <t>3,709</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>21,882</t>
+          <t>21,605</t>
         </is>
       </c>
     </row>
@@ -6624,37 +6624,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>아모레퍼시픽홀딩스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>28,050</t>
+          <t>188,800</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>하락300</t>
+          <t>하락7,500</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>24,231</t>
+          <t>47,359</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>9,061</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>21,447</t>
+          <t>21,428</t>
         </is>
       </c>
     </row>
@@ -6664,37 +6664,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>아모레퍼시픽홀딩스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>123,500</t>
+          <t>27,850</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>상승600</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>7,538</t>
+          <t>96,300</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>2,709</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>21,346</t>
+          <t>21,294</t>
         </is>
       </c>
     </row>
@@ -6709,32 +6709,32 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>40,200</t>
+          <t>39,950</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>하락2,000</t>
+          <t>하락2,250</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>-4.74%</t>
+          <t>-5.33%</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>38,381</t>
+          <t>147,994</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1,549</t>
+          <t>5,939</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>21,343</t>
+          <t>21,210</t>
         </is>
       </c>
     </row>
@@ -6749,32 +6749,32 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>84,500</t>
+          <t>83,800</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>하락2,300</t>
+          <t>하락3,000</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>17,511</t>
+          <t>73,495</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1,487</t>
+          <t>6,201</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>19,121</t>
+          <t>18,963</t>
         </is>
       </c>
     </row>
@@ -6789,32 +6789,32 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>163,400</t>
+          <t>161,200</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>상승1,800</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>9,393</t>
+          <t>26,955</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1,525</t>
+          <t>4,371</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>18,932</t>
+          <t>18,678</t>
         </is>
       </c>
     </row>
@@ -6829,32 +6829,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>77,900</t>
+          <t>77,000</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>하락1,700</t>
+          <t>하락2,600</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>44,018</t>
+          <t>157,589</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>3,453</t>
+          <t>12,258</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>18,388</t>
+          <t>18,176</t>
         </is>
       </c>
     </row>
@@ -6864,37 +6864,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SK아이이테크놀로지</t>
+          <t>동원산업</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>21,600</t>
+          <t>39,650</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>하락500</t>
+          <t>하락350</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>39,113</t>
+          <t>31,288</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>1,247</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>17,666</t>
+          <t>17,505</t>
         </is>
       </c>
     </row>
@@ -6904,37 +6904,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>동원산업</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>39,950</t>
+          <t>20,850</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>하락50</t>
+          <t>상승250</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>8,625</t>
+          <t>151,152</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>3,172</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>17,637</t>
+          <t>17,432</t>
         </is>
       </c>
     </row>
@@ -6944,37 +6944,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>150,700</t>
+          <t>6,040</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>상승1,700</t>
+          <t>하락180</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>10,317</t>
+          <t>278,609</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1,549</t>
+          <t>1,699</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>17,612</t>
+          <t>17,351</t>
         </is>
       </c>
     </row>
@@ -6984,37 +6984,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>148,000</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>하락120</t>
+          <t>하락1,000</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>87,229</t>
+          <t>32,524</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>4,862</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>17,523</t>
+          <t>17,296</t>
         </is>
       </c>
     </row>
@@ -7024,37 +7024,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>SK아이이테크놀로지</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>20,750</t>
+          <t>21,050</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>상승150</t>
+          <t>하락1,050</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>23,721</t>
+          <t>153,574</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>3,279</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>17,349</t>
+          <t>17,216</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>391,500</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>상승6,500</t>
+          <t>상승4,000</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>+1.69%</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>11,324</t>
+          <t>34,967</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4,468</t>
+          <t>13,791</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>16,943</t>
+          <t>16,835</t>
         </is>
       </c>
     </row>
@@ -7109,32 +7109,32 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>42,000</t>
+          <t>41,750</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>하락700</t>
+          <t>하락950</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>48,208</t>
+          <t>155,004</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2,030</t>
+          <t>6,497</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>16,484</t>
+          <t>16,386</t>
         </is>
       </c>
     </row>
@@ -7144,37 +7144,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>오리온홀딩스</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>17,290</t>
+          <t>25,450</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>상승320</t>
+          <t>상승600</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>204,796</t>
+          <t>303,850</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>3,538</t>
+          <t>7,684</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>16,016</t>
+          <t>15,943</t>
         </is>
       </c>
     </row>
@@ -7184,37 +7184,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>오리온홀딩스</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>상승50</t>
+          <t>상승30</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>29,305</t>
+          <t>530,323</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>9,145</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>15,599</t>
+          <t>15,747</t>
         </is>
       </c>
     </row>
@@ -7224,37 +7224,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>대웅</t>
+          <t>오뚜기</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>25,250</t>
+          <t>362,000</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>상승950</t>
+          <t>하락8,500</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>36,858</t>
+          <t>4,586</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1,670</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>14,681</t>
+          <t>14,508</t>
         </is>
       </c>
     </row>
@@ -7264,37 +7264,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>오뚜기</t>
+          <t>대웅</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>365,000</t>
+          <t>24,250</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>하락5,500</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1,253</t>
+          <t>96,029</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>2,386</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>14,629</t>
+          <t>14,099</t>
         </is>
       </c>
     </row>
@@ -7304,37 +7304,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>태광산업</t>
+          <t>롯데정밀화학</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1,198,000</t>
+          <t>51,300</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>하락13,000</t>
+          <t>상승700</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>75,642</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>3,914</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>13,339</t>
+          <t>13,235</t>
         </is>
       </c>
     </row>
@@ -7344,37 +7344,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>롯데정밀화학</t>
+          <t>태광산업</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>51,400</t>
+          <t>1,168,000</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>상승800</t>
+          <t>하락43,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>+1.58%</t>
+          <t>-3.55%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>17,398</t>
+          <t>1,896</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>2,252</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>13,261</t>
+          <t>13,005</t>
         </is>
       </c>
     </row>
@@ -7389,32 +7389,32 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>93,800</t>
+          <t>90,800</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>상승4,000</t>
+          <t>상승1,000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>21,324</t>
+          <t>47,881</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1,966</t>
+          <t>4,435</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>12,947</t>
+          <t>12,533</t>
         </is>
       </c>
     </row>
@@ -7429,32 +7429,32 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>59,800</t>
+          <t>59,300</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>상승1,600</t>
+          <t>상승1,100</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>62,697</t>
+          <t>133,304</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>3,777</t>
+          <t>7,985</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>12,532</t>
+          <t>12,427</t>
         </is>
       </c>
     </row>
@@ -7469,32 +7469,32 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>16,720</t>
+          <t>16,610</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>하락290</t>
+          <t>하락400</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>23,238</t>
+          <t>95,847</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>1,598</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>12,297</t>
+          <t>12,216</t>
         </is>
       </c>
     </row>
@@ -7509,32 +7509,32 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>16,540</t>
+          <t>16,530</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>하락120</t>
+          <t>하락130</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>49,575</t>
+          <t>110,392</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1,827</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>11,600</t>
+          <t>11,593</t>
         </is>
       </c>
     </row>
@@ -7549,32 +7549,32 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>61,700</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>하락1,100</t>
+          <t>하락1,900</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-3.03%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>14,263</t>
+          <t>44,025</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>2,711</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>11,154</t>
+          <t>11,009</t>
         </is>
       </c>
     </row>
@@ -7589,32 +7589,32 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>118,500</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>하락2,900</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3,874</t>
+          <t>19,076</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>2,246</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>10,995</t>
+          <t>10,856</t>
         </is>
       </c>
     </row>
@@ -7629,32 +7629,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>50,100</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>5,615</t>
+          <t>28,420</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1,425</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>10,608</t>
+          <t>10,587</t>
         </is>
       </c>
     </row>
@@ -7664,37 +7664,37 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>지역난방공사</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>91,300</t>
+          <t>113,700</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>하락1,100</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>11,950</t>
+          <t>20,975</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>2,391</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>10,571</t>
+          <t>10,579</t>
         </is>
       </c>
     </row>
@@ -7704,37 +7704,37 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>지역난방공사</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>113,400</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>하락1,400</t>
+          <t>하락1,200</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>3,648</t>
+          <t>52,633</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>4,767</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>10,551</t>
+          <t>10,421</t>
         </is>
       </c>
     </row>
@@ -7749,32 +7749,32 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>43,350</t>
+          <t>42,650</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>하락250</t>
+          <t>하락950</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>4,478</t>
+          <t>14,145</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>608</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>10,202</t>
+          <t>10,037</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>222,000</t>
+          <t>219,500</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락5,000</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2,246</t>
+          <t>10,107</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>2,258</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>9,945</t>
+          <t>9,833</t>
         </is>
       </c>
     </row>
@@ -7829,32 +7829,32 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>8,050</t>
+          <t>7,930</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>상승120</t>
+          <t>보합0</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>81,067</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>647</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9,801</t>
+          <t>9,655</t>
         </is>
       </c>
     </row>
@@ -7869,32 +7869,32 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>55,600</t>
+          <t>54,200</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>하락600</t>
+          <t>하락2,000</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>10,360</t>
+          <t>43,206</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>2,383</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>9,618</t>
+          <t>9,376</t>
         </is>
       </c>
     </row>
@@ -7909,32 +7909,32 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>133,200</t>
+          <t>137,400</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>상승1,700</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>7,695</t>
+          <t>68,921</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>1,035</t>
+          <t>9,531</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>8,658</t>
+          <t>8,931</t>
         </is>
       </c>
     </row>
@@ -7949,32 +7949,32 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>60,600</t>
+          <t>60,100</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>하락800</t>
+          <t>하락1,300</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>-1.30%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4,751</t>
+          <t>20,691</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1,251</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>8,399</t>
+          <t>8,330</t>
         </is>
       </c>
     </row>
@@ -7984,37 +7984,37 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>세아제강지주</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>7,440</t>
+          <t>192,300</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>상승100</t>
+          <t>상승5,500</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>134,781</t>
+          <t>49,657</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>9,396</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>7,980</t>
+          <t>7,964</t>
         </is>
       </c>
     </row>
@@ -8024,37 +8024,37 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>세아제강지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>188,500</t>
+          <t>7,210</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>상승1,700</t>
+          <t>하락130</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>17,231</t>
+          <t>353,201</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>3,238</t>
+          <t>2,591</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>7,807</t>
+          <t>7,733</t>
         </is>
       </c>
     </row>
@@ -8069,32 +8069,32 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>26,200</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>하락200</t>
+          <t>하락450</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>13,194</t>
+          <t>30,662</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>807</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>7,668</t>
+          <t>7,596</t>
         </is>
       </c>
     </row>
@@ -8109,32 +8109,32 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>18,480</t>
+          <t>18,390</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>하락180</t>
+          <t>하락270</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>14,821</t>
+          <t>53,668</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>993</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>7,554</t>
+          <t>7,518</t>
         </is>
       </c>
     </row>
@@ -8149,32 +8149,32 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>11,980</t>
+          <t>11,760</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>하락20</t>
+          <t>하락240</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-2.00%</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>45,930</t>
+          <t>223,084</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>2,651</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>7,410</t>
+          <t>7,274</t>
         </is>
       </c>
     </row>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>20,950</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>하락100</t>
+          <t>하락350</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>38,298</t>
+          <t>117,983</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>2,453</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>7,259</t>
+          <t>7,172</t>
         </is>
       </c>
     </row>
@@ -8229,32 +8229,32 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>14,130</t>
+          <t>14,100</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>보합0</t>
+          <t>하락30</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>29,330</t>
+          <t>96,140</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>1,362</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>6,645</t>
+          <t>6,631</t>
         </is>
       </c>
     </row>
@@ -8269,32 +8269,32 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>135,700</t>
+          <t>136,400</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>하락900</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1,582</t>
+          <t>2,448</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>6,446</t>
+          <t>6,479</t>
         </is>
       </c>
     </row>
@@ -8309,32 +8309,32 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>126,000</t>
+          <t>124,400</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>하락2,500</t>
+          <t>하락4,100</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1,963</t>
+          <t>2,747</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>6,300</t>
+          <t>6,220</t>
         </is>
       </c>
     </row>
@@ -8349,32 +8349,32 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>23,650</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>상승300</t>
+          <t>하락50</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>29,921</t>
+          <t>87,538</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>2,096</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>5,952</t>
+          <t>5,865</t>
         </is>
       </c>
     </row>
@@ -8384,37 +8384,37 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>코스모화학</t>
+          <t>아세아</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>15,310</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>상승120</t>
+          <t>하락500</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>74,150</t>
+          <t>1,948</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>1,133</t>
+          <t>535</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>5,880</t>
+          <t>5,762</t>
         </is>
       </c>
     </row>
@@ -8424,37 +8424,37 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>아세아</t>
+          <t>코스모화학</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>272,500</t>
+          <t>14,990</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>하락6,000</t>
+          <t>하락200</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-1.32%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>180,863</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2,747</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>5,648</t>
+          <t>5,757</t>
         </is>
       </c>
     </row>
